--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,43 +656,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
@@ -704,100 +705,112 @@
         <v>45016</v>
       </c>
       <c r="J7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1449800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1470900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1439000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
+      <c r="G8" s="3">
+        <v>1377700</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1368700</v>
       </c>
       <c r="I8" s="3">
         <v>1317000</v>
       </c>
       <c r="J8" s="3">
+        <v>1092800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1337100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>635200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>624100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>621500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>595600</v>
+      </c>
+      <c r="H9" s="3">
+        <v>598300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>592100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>514400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>814600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>846900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>817500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>782100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>770400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>724900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>578400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -832,14 +846,17 @@
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
+      <c r="J12" s="3">
+        <v>2800</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,48 +884,54 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>-8300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
+        <v>92300</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E15" s="3">
         <v>36300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>35400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>36000</v>
       </c>
       <c r="G15" s="3">
         <v>35500</v>
@@ -920,13 +943,16 @@
         <v>34700</v>
       </c>
       <c r="J15" s="3">
+        <v>33300</v>
+      </c>
+      <c r="K15" s="3">
         <v>35900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1370800</v>
+        <v>1379400</v>
       </c>
       <c r="E17" s="3">
+        <v>1368900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1363200</v>
       </c>
-      <c r="F17" s="3">
-        <v>1337200</v>
-      </c>
       <c r="G17" s="3">
-        <v>1331800</v>
+        <v>1312700</v>
       </c>
       <c r="H17" s="3">
-        <v>1300900</v>
+        <v>1291100</v>
       </c>
       <c r="I17" s="3">
-        <v>1269900</v>
+        <v>1270000</v>
       </c>
       <c r="J17" s="3">
+        <v>1040300</v>
+      </c>
+      <c r="K17" s="3">
         <v>1301800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>100100</v>
+        <v>70400</v>
       </c>
       <c r="E18" s="3">
+        <v>102000</v>
+      </c>
+      <c r="F18" s="3">
         <v>75800</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
+      <c r="G18" s="3">
+        <v>65000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>77700</v>
       </c>
       <c r="I18" s="3">
-        <v>47100</v>
+        <v>47000</v>
       </c>
       <c r="J18" s="3">
+        <v>52500</v>
+      </c>
+      <c r="K18" s="3">
         <v>35300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,16 +1039,17 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>-2800</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
@@ -1023,60 +1057,66 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>-500</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>163400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>136700</v>
+        <v>110000</v>
       </c>
       <c r="E21" s="3">
+        <v>138600</v>
+      </c>
+      <c r="F21" s="3">
         <v>111200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="G21" s="3">
+        <v>100500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>112900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>81800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>85800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E22" s="3">
         <v>18200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>18500</v>
       </c>
       <c r="G22" s="3">
         <v>19000</v>
@@ -1088,24 +1128,27 @@
         <v>18100</v>
       </c>
       <c r="J22" s="3">
+        <v>28700</v>
+      </c>
+      <c r="K22" s="3">
         <v>20700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E23" s="3">
         <v>82200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>56600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>8800</v>
       </c>
       <c r="G23" s="3">
         <v>46000</v>
@@ -1117,24 +1160,27 @@
         <v>29000</v>
       </c>
       <c r="J23" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="K23" s="3">
         <v>177900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-2000</v>
       </c>
       <c r="G24" s="3">
         <v>7300</v>
@@ -1146,13 +1192,16 @@
         <v>5200</v>
       </c>
       <c r="J24" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="K24" s="3">
         <v>29400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E26" s="3">
         <v>67000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>45900</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
+      <c r="G26" s="3">
+        <v>38700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>55700</v>
       </c>
       <c r="I26" s="3">
         <v>23800</v>
       </c>
       <c r="J26" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="K26" s="3">
         <v>148500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E27" s="3">
         <v>42800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27000</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
+      <c r="G27" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>33100</v>
       </c>
       <c r="I27" s="3">
         <v>4100</v>
       </c>
       <c r="J27" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="K27" s="3">
         <v>148500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1325,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,16 +1421,19 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>2800</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
@@ -1371,49 +1441,55 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>500</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-163400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E33" s="3">
         <v>42800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27000</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>4</v>
+      <c r="G33" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>33100</v>
       </c>
       <c r="I33" s="3">
         <v>4100</v>
       </c>
       <c r="J33" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="K33" s="3">
         <v>148500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,53 +1517,59 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E35" s="3">
         <v>42800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27000</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>4</v>
+      <c r="G35" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>33100</v>
       </c>
       <c r="I35" s="3">
         <v>4100</v>
       </c>
       <c r="J35" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="K35" s="3">
         <v>148500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
@@ -1499,13 +1581,16 @@
         <v>45016</v>
       </c>
       <c r="J38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,20 +1616,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>563100</v>
+      </c>
+      <c r="E41" s="3">
         <v>334500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>372800</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1553,25 +1640,28 @@
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
+      <c r="J41" s="3">
+        <v>59700</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -1588,19 +1678,22 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>754900</v>
+      </c>
+      <c r="E43" s="3">
         <v>752600</v>
       </c>
-      <c r="E43" s="3">
-        <v>764200</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+      <c r="F43" s="3">
+        <v>788300</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -1611,26 +1704,29 @@
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>532000</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E44" s="3">
         <v>105000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>106000</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1640,25 +1736,28 @@
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
+      <c r="J44" s="3">
+        <v>84800</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>309200</v>
+        <v>134900</v>
       </c>
       <c r="E45" s="3">
-        <v>247700</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
+        <v>158500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>109600</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>4</v>
@@ -1669,26 +1768,29 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="J45" s="3">
+        <v>97700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1690700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1501300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1490600</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1698,55 +1800,61 @@
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
+      <c r="J46" s="3">
+        <v>860400</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>9900</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2008300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1999200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1996300</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1756,14 +1864,17 @@
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>839900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1771,28 +1882,31 @@
         <v>928900</v>
       </c>
       <c r="E49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="F49" s="3">
         <v>929000</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>899900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,19 +1966,22 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>179200</v>
+        <v>134000</v>
       </c>
       <c r="E52" s="3">
-        <v>176900</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
+        <v>136600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>134700</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
@@ -1872,14 +1992,17 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>50100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,20 +2030,23 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4800000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4608700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4592900</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>4</v>
       </c>
@@ -1930,14 +2056,17 @@
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
+      <c r="J54" s="3">
+        <v>2746300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,20 +2092,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>368900</v>
+      </c>
+      <c r="E57" s="3">
         <v>371100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>383100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>4</v>
       </c>
@@ -1985,54 +2116,60 @@
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="J57" s="3">
+        <v>230400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E58" s="3">
         <v>10700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>16900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>526700</v>
+        <v>42100</v>
       </c>
       <c r="E59" s="3">
-        <v>435000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
+        <v>46000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>101900</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>4</v>
@@ -2043,26 +2180,29 @@
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>120600</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>887300</v>
+      </c>
+      <c r="E60" s="3">
         <v>908600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>834800</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2072,25 +2212,28 @@
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
+      <c r="J60" s="3">
+        <v>624800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1082000</v>
+        <v>2240200</v>
       </c>
       <c r="E61" s="3">
-        <v>1167000</v>
+        <v>2237900</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2327600</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2102,24 +2245,27 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1251900</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1455500</v>
+        <v>285600</v>
       </c>
       <c r="E62" s="3">
-        <v>1476000</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
+        <v>299500</v>
+      </c>
+      <c r="F62" s="3">
+        <v>315400</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -2130,14 +2276,17 @@
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="J62" s="3">
+        <v>157700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,19 +2378,22 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3868800</v>
+        <v>3413100</v>
       </c>
       <c r="E66" s="3">
-        <v>3893800</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
+        <v>3446000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>3477800</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>4</v>
@@ -2246,14 +2404,17 @@
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
+      <c r="J66" s="3">
+        <v>2034400</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,20 +2552,23 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>251600</v>
+      </c>
+      <c r="E72" s="3">
         <v>225300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>182500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2404,14 +2578,17 @@
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
+      <c r="J72" s="3">
+        <v>-167200</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1005900</v>
+      </c>
+      <c r="E76" s="3">
         <v>739900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>699200</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="I76" s="3">
+        <v>639100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>331600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,24 +2744,27 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
@@ -2584,42 +2776,48 @@
         <v>45016</v>
       </c>
       <c r="J80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E81" s="3">
         <v>42800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27000</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
+      <c r="G81" s="3">
+        <v>20800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>33100</v>
       </c>
       <c r="I81" s="3">
         <v>4100</v>
       </c>
       <c r="J81" s="3">
+        <v>-72500</v>
+      </c>
+      <c r="K81" s="3">
         <v>148500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>36300</v>
+        <v>34700</v>
       </c>
       <c r="E83" s="3">
-        <v>35400</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+        <v>34700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>33300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>37700</v>
+      </c>
+      <c r="H83" s="3">
+        <v>36100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>36100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>32700</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E89" s="3">
         <v>120400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
+      <c r="G89" s="3">
+        <v>88700</v>
+      </c>
+      <c r="H89" s="3">
+        <v>43200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>96300</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38900</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-23800</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-33600</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-21300</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-68700</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31600</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-61700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3335,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-119800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18500</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
+      <c r="G100" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-35900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>228600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-64800</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
+      <c r="G102" s="3">
+        <v>40000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-1300</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -656,161 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1606300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1449800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1470900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1439000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>1346000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1377700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1368700</v>
       </c>
-      <c r="I8" s="3">
-        <v>1317000</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1092800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1337100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>654000</v>
+      </c>
+      <c r="E9" s="3">
         <v>635200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>624100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>621500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>598100</v>
+      </c>
+      <c r="I9" s="3">
         <v>595600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>598300</v>
       </c>
-      <c r="I9" s="3">
-        <v>592100</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>514400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>952300</v>
+      </c>
+      <c r="E10" s="3">
         <v>814600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>846900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>817500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>747900</v>
+      </c>
+      <c r="I10" s="3">
         <v>782100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>770400</v>
       </c>
-      <c r="I10" s="3">
-        <v>724900</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>578400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,17 +858,20 @@
       <c r="I12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
         <v>2800</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,72 +902,81 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-8300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>92300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E15" s="3">
         <v>36800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>35400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>36000</v>
+      </c>
+      <c r="I15" s="3">
         <v>35500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>34700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
+        <v>33300</v>
+      </c>
+      <c r="L15" s="3">
+        <v>35900</v>
+      </c>
+      <c r="M15" s="3">
         <v>34700</v>
       </c>
-      <c r="J15" s="3">
-        <v>33300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>35900</v>
-      </c>
-      <c r="L15" s="3">
-        <v>34700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +986,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1448700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1379400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1368900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1363200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>1319800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1312700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1291100</v>
       </c>
-      <c r="I17" s="3">
-        <v>1270000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1040300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1301800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E18" s="3">
         <v>70400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>102000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>75800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>26200</v>
+      </c>
+      <c r="I18" s="3">
         <v>65000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>77700</v>
       </c>
-      <c r="I18" s="3">
-        <v>47000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>52500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,168 +1071,184 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>163400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E21" s="3">
         <v>110000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>138600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>111200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>61700</v>
+      </c>
+      <c r="I21" s="3">
         <v>100500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>112900</v>
       </c>
-      <c r="I21" s="3">
-        <v>81800</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E22" s="3">
         <v>14600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I22" s="3">
         <v>19000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>18700</v>
       </c>
-      <c r="I22" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>167200</v>
+      </c>
+      <c r="E23" s="3">
         <v>57100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>82200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>56600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I23" s="3">
         <v>46000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>67800</v>
       </c>
-      <c r="I23" s="3">
-        <v>29000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-68500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>177900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E24" s="3">
         <v>11100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>12100</v>
       </c>
-      <c r="I24" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>29400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1279,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>140900</v>
+      </c>
+      <c r="E26" s="3">
         <v>46000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>67000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I26" s="3">
         <v>38700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>55700</v>
       </c>
-      <c r="I26" s="3">
-        <v>23800</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-64400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>148500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E27" s="3">
         <v>26300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>42800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I27" s="3">
         <v>20800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>33100</v>
       </c>
-      <c r="I27" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-72500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>148500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1489,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-163400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E33" s="3">
         <v>26300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>42800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I33" s="3">
         <v>20800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>33100</v>
       </c>
-      <c r="I33" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-72500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>148500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1594,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E35" s="3">
         <v>26300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>42800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I35" s="3">
         <v>20800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>33100</v>
       </c>
-      <c r="I35" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-72500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>148500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,57 +1701,61 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>556800</v>
+      </c>
+      <c r="E41" s="3">
         <v>563100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>334500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>372800</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
+      <c r="H41" s="3">
+        <v>437600</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>59700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E42" s="3">
         <v>9500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1681,136 +1769,151 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>810000</v>
+      </c>
+      <c r="E43" s="3">
         <v>754900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>752600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>788300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>834600</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>532000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E44" s="3">
         <v>108200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>105000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>106000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
+      <c r="H44" s="3">
+        <v>105500</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>84800</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>227200</v>
+      </c>
+      <c r="E45" s="3">
         <v>134900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>158500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>109600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>147200</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>97700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1832800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1690700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1501300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1490600</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
+      <c r="H46" s="3">
+        <v>1618100</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>860400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1818,16 +1921,16 @@
         <v>3300</v>
       </c>
       <c r="E47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F47" s="3">
         <v>7900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9900</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
+      <c r="H47" s="3">
+        <v>9100</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
@@ -1835,78 +1938,87 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2039000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2008300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1999200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1996300</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
+      <c r="H48" s="3">
+        <v>2012200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>839900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>928900</v>
+        <v>929000</v>
       </c>
       <c r="E49" s="3">
         <v>928900</v>
       </c>
       <c r="F49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="G49" s="3">
         <v>929000</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>921600</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>899900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2084,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E52" s="3">
         <v>134000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>136600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>134700</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>138000</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>50100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2154,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4956100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4800000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4608700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4592900</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
+      <c r="H54" s="3">
+        <v>4731600</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>2746300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2221,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>401200</v>
+      </c>
+      <c r="E57" s="3">
         <v>368900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>371100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>383100</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
+      <c r="H57" s="3">
+        <v>474500</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>230400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E58" s="3">
         <v>12200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16600</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>16900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>124700</v>
+      </c>
+      <c r="E59" s="3">
         <v>42100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>101900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>97200</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>120600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>945400</v>
+      </c>
+      <c r="E60" s="3">
         <v>887300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>908600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>834800</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
+      <c r="H60" s="3">
+        <v>994100</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>624800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2226600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2240200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2237900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2327600</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2335600</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1251900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>261700</v>
+      </c>
+      <c r="E62" s="3">
         <v>285600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>299500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>315400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>319600</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>157700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2534,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3433700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3413100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3446000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3477800</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
+      <c r="H66" s="3">
+        <v>3649200</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>2034400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2724,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>365800</v>
+      </c>
+      <c r="E72" s="3">
         <v>251600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>225300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>182500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
+      <c r="H72" s="3">
+        <v>155500</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-167200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2864,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1131400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1005900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>739900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>699200</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
-        <v>639100</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="H76" s="3">
+        <v>670900</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>331600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2934,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E81" s="3">
         <v>26300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>42800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I81" s="3">
         <v>20800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>33100</v>
       </c>
-      <c r="I81" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-72500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>148500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3026,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F83" s="3">
         <v>34700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>34700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>33300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>37700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>36100</v>
       </c>
-      <c r="I83" s="3">
-        <v>36100</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32700</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E89" s="3">
         <v>89700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>120400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>67500</v>
+      </c>
+      <c r="I89" s="3">
         <v>88700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>43200</v>
       </c>
-      <c r="I89" s="3">
-        <v>22300</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>96300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3286,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-81300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-33600</v>
       </c>
-      <c r="I91" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-68700</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3389,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-35100</v>
       </c>
-      <c r="I94" s="3">
-        <v>-21400</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3441,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3236,14 +3468,17 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3579,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E100" s="3">
         <v>183400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-119800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="I100" s="3">
         <v>-23900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-56000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-4400</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-35900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3396,42 +3643,48 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E102" s="3">
         <v>228600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-38200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-64800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I102" s="3">
         <v>40000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-47900</v>
       </c>
-      <c r="I102" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -656,172 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43465</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1497200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1606300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1449800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1470900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1439000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1346000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1377700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1368700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1092800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1337100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>657700</v>
+      </c>
+      <c r="E9" s="3">
         <v>654000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>635200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>624100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>621500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>598100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>595600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>598300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>514400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>839600</v>
+      </c>
+      <c r="E10" s="3">
         <v>952300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>814600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>846900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>817500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>747900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>782100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>770400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>578400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +848,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -861,17 +875,20 @@
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
         <v>2800</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,78 +922,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>-21500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-8300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>92300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E15" s="3">
         <v>37900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>36800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>33300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,78 +1013,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1430100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1448700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1379400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1368900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1363200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1319800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1312700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1291100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1040300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1301800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E18" s="3">
         <v>157600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>70400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>102000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>75800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>65000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>77700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>52500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,183 +1105,199 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>163400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E21" s="3">
         <v>197200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>110000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>138600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>111200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>61700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>100500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>112900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>85800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E22" s="3">
         <v>13500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E23" s="3">
         <v>167200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>57100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>82200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>56600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>67800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-68500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>177900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E24" s="3">
         <v>26400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1331,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E26" s="3">
         <v>140900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>67000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>55700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>148500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E27" s="3">
         <v>114200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>42800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>33100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-72500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>148500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,78 +1559,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-163400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E33" s="3">
         <v>114200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>42800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>33100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-72500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>148500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1673,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E35" s="3">
         <v>114200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>42800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>33100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-72500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>148500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43465</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,64 +1788,68 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E41" s="3">
         <v>556800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>563100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>334500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>372800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>437600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>59700</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>9900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1772,253 +1862,277 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>829100</v>
+      </c>
+      <c r="E43" s="3">
         <v>810000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>754900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>752600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>788300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>834600</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>532000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E44" s="3">
         <v>115100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>108200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>105000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>106000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>105500</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>84800</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>177800</v>
+      </c>
+      <c r="E45" s="3">
         <v>227200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>134900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>158500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>147200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>97700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1761300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1832800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1690700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1501300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1490600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1618100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>860400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3300</v>
+        <v>1400</v>
       </c>
       <c r="E47" s="3">
         <v>3300</v>
       </c>
       <c r="F47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G47" s="3">
         <v>7900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2063700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2039000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2008300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1999200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1996300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2012200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>839900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>953500</v>
+      </c>
+      <c r="E49" s="3">
         <v>929000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>928900</v>
       </c>
       <c r="F49" s="3">
         <v>928900</v>
       </c>
       <c r="G49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="H49" s="3">
         <v>929000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>921600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>899900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,43 +2204,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E52" s="3">
         <v>139700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>134000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>136600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>134700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>138000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>50100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,43 +2280,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4911300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4956100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4800000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4608700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4592900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4731600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>2746300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,218 +2352,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>371900</v>
+      </c>
+      <c r="E57" s="3">
         <v>401200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>368900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>371100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>383100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>474500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>230400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E58" s="3">
         <v>55600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>61000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>16900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E59" s="3">
         <v>124700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>101900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>97200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>120600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>830100</v>
+      </c>
+      <c r="E60" s="3">
         <v>945400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>887300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>908600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>834800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>994100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>624800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2263000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2226600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2240200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2237900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2327600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2335600</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1251900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>253700</v>
+      </c>
+      <c r="E62" s="3">
         <v>261700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>285600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>299500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>315400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>319600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>157700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,43 +2692,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3346800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3433700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3413100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3446000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3477800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3649200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>2034400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,43 +2898,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E72" s="3">
         <v>365800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>251600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>225300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>182500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>155500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-167200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,43 +3050,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1175200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1131400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1005900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>739900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>699200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>670900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>331600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3126,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43465</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E81" s="3">
         <v>114200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>42800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>33100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-72500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>148500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,43 +3225,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E83" s="3">
         <v>36000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>35500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>34700</v>
       </c>
       <c r="G83" s="3">
         <v>34700</v>
       </c>
       <c r="H83" s="3">
+        <v>34700</v>
+      </c>
+      <c r="I83" s="3">
         <v>33300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>37700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>36100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32700</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E89" s="3">
         <v>119600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>89700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>120400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>67500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>43200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>96300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,43 +3507,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68700</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3619,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-105400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-24800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3675,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3471,14 +3705,17 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,43 +3825,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>183400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-119800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-56000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3646,45 +3895,51 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>228600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-38200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-64800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-47900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -656,185 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1645300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1497200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1606300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1449800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1470900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1439000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1346000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1377700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1368700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1092800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1337100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>671700</v>
+      </c>
+      <c r="E9" s="3">
         <v>657700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>654000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>635200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>624100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>621500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>598100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>595600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>598300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>514400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>973600</v>
+      </c>
+      <c r="E10" s="3">
         <v>839600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>952300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>814600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>846900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>817500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>747900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>782100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>770400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>578400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -878,17 +892,20 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,84 +942,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>600</v>
       </c>
       <c r="E14" s="3">
         <v>-21500</v>
       </c>
       <c r="F14" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-8300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>92300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E15" s="3">
         <v>36200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>37900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>35400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>34700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1040,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1508000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1430100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1448700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1379400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1368900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1363200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1319800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1312700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1291100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1040300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1301800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E18" s="3">
         <v>67100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>157600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>70400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>102000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>75800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>77700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>52500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,198 +1139,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-21300</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-300</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>163400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>124600</v>
+        <v>176600</v>
       </c>
       <c r="E21" s="3">
+        <v>103100</v>
+      </c>
+      <c r="F21" s="3">
         <v>197200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>110000</v>
       </c>
-      <c r="G21" s="3">
-        <v>138600</v>
-      </c>
       <c r="H21" s="3">
+        <v>138300</v>
+      </c>
+      <c r="I21" s="3">
         <v>111200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>61700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>112900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>85800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E22" s="3">
         <v>14200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E23" s="3">
         <v>74200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>167200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>57100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>82200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>56600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>67800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-68500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>177900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E24" s="3">
         <v>15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E26" s="3">
         <v>59000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>140900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>67000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>45900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>55700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>148500</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E27" s="3">
         <v>41400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>114200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>42800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-72500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>148500</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,84 +1629,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>21300</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3">
-        <v>300</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-163400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E33" s="3">
         <v>41400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>114200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>42800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-72500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>148500</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E35" s="3">
         <v>41400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>114200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>42800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-72500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>148500</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,70 +1875,74 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>540600</v>
+      </c>
+      <c r="E41" s="3">
         <v>495000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>556800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>563100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>334500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>372800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>437600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>59700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>16000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -1865,274 +1955,298 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>831600</v>
+      </c>
+      <c r="E43" s="3">
         <v>829100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>810000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>754900</v>
       </c>
-      <c r="G43" s="3">
-        <v>752600</v>
-      </c>
       <c r="H43" s="3">
+        <v>762600</v>
+      </c>
+      <c r="I43" s="3">
         <v>788300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>834600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>532000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E44" s="3">
         <v>120400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>115100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>108200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>105000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>106000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>84800</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E45" s="3">
         <v>177800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>227200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>134900</v>
       </c>
-      <c r="G45" s="3">
-        <v>158500</v>
-      </c>
       <c r="H45" s="3">
+        <v>148500</v>
+      </c>
+      <c r="I45" s="3">
         <v>109600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>147200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>97700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1877100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1761300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1832800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1690700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1501300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1490600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1618100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>860400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>1400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3300</v>
       </c>
       <c r="F47" s="3">
         <v>3300</v>
       </c>
       <c r="G47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H47" s="3">
         <v>7900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2067300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2063700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2039000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2008300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1999200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1996300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2012200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>839900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>954600</v>
+      </c>
+      <c r="E49" s="3">
         <v>953500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>929000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>928900</v>
       </c>
       <c r="G49" s="3">
         <v>928900</v>
       </c>
       <c r="H49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="I49" s="3">
         <v>929000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>921600</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>899900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,46 +2324,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E52" s="3">
         <v>115600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>139700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>134000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>136600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>134700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>50100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,46 +2406,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5027300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4911300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4956100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4800000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4608700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4592900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4731600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>2746300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,236 +2483,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>364500</v>
+      </c>
+      <c r="E57" s="3">
         <v>371900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>401200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>368900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>371100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>383100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>474500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>230400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E58" s="3">
         <v>17900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>55600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>61000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>16900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E59" s="3">
         <v>28300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>124700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>101900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>97200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>120600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>880900</v>
+      </c>
+      <c r="E60" s="3">
         <v>830100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>945400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>887300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>908600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>834800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>994100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>624800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2255200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2263000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2226600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2240200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2237900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2327600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2335600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1251900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>244900</v>
+      </c>
+      <c r="E62" s="3">
         <v>253700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>261700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>285600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>299500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>315400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>319600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>157700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,46 +2850,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3380900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3346800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3433700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3413100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3446000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3477800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3649200</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>2034400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,46 +3072,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>480100</v>
+      </c>
+      <c r="E72" s="3">
         <v>407200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>365800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>251600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>225300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>182500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>155500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-167200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,46 +3236,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1254600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1175200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1131400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1005900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>739900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>699200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>670900</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>331600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E81" s="3">
         <v>41400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>114200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>42800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-72500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>148500</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,46 +3424,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E83" s="3">
         <v>35400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>34700</v>
       </c>
       <c r="H83" s="3">
         <v>34700</v>
       </c>
       <c r="I83" s="3">
+        <v>34700</v>
+      </c>
+      <c r="J83" s="3">
         <v>33300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>37700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32700</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>119600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>89700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>120400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>43200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>96300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,46 +3728,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-81300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-57400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-68700</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-44500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-38900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3708,14 +3942,17 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>183400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-119800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-35900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3898,48 +4147,54 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>228600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-38200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-64800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-47900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1605100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1576700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1645300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1497200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1606300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1449800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1470900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1439000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1346000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1377700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1368700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1092800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1337100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>651400</v>
+      </c>
+      <c r="E9" s="3">
         <v>677000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>671700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>657700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>654000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>635200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>624100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>621500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>598100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>595600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>598300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>514400</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>953700</v>
+      </c>
+      <c r="E10" s="3">
         <v>899800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>973600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>839600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>952300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>814600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>846900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>817500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>747900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>782100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>770400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>578400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -912,17 +925,20 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,96 +981,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>4700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-21500</v>
       </c>
       <c r="G14" s="3">
         <v>-21500</v>
       </c>
       <c r="H14" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>-1600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>-8300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>92300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E15" s="3">
         <v>39200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>36200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>34700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>33300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1093,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1560300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1508000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1430100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1448700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1379400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1368900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1363200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1319800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1312700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1291100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1040300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1301800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E18" s="3">
         <v>16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>137300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>67100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>157600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>70400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>102000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>75800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>77700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>52500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,25 +1206,26 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-1800</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1200,202 +1233,217 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>163400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E21" s="3">
         <v>55600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>176600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>103100</v>
       </c>
-      <c r="G21" s="3">
-        <v>197200</v>
-      </c>
       <c r="H21" s="3">
+        <v>195300</v>
+      </c>
+      <c r="I21" s="3">
         <v>107200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>138300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>111200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>112900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>85800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E22" s="3">
         <v>13900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>122000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>74200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>167200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>82200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>56600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>67800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-68500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>177900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1486,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>95700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>59000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>140900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>67000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>45900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>38700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>55700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>73000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>114200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>42800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-72500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>148500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,25 +1768,28 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>1800</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>-100</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -1728,70 +1797,76 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-163400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>73000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>114200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>42800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>33100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-72500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>148500</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1909,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>73000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>114200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>42800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>33100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-72500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>148500</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,82 +2048,86 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>709600</v>
+      </c>
+      <c r="E41" s="3">
         <v>609400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>540600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>495000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>556800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>563100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>334500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>372800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>437600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>59700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E42" s="3">
         <v>4900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2051,184 +2140,199 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>771700</v>
+      </c>
+      <c r="E43" s="3">
         <v>772200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>831600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>829100</v>
       </c>
-      <c r="G43" s="3">
-        <v>810000</v>
-      </c>
       <c r="H43" s="3">
+        <v>797300</v>
+      </c>
+      <c r="I43" s="3">
         <v>754900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>762600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>788300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>834600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>532000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E44" s="3">
         <v>121600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>118400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>120400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>115100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>108200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>106000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>105500</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>84800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>343400</v>
+      </c>
+      <c r="E45" s="3">
         <v>318500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>251000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>177800</v>
       </c>
-      <c r="G45" s="3">
-        <v>227200</v>
-      </c>
       <c r="H45" s="3">
+        <v>239900</v>
+      </c>
+      <c r="I45" s="3">
         <v>134900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>148500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>109600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>147200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>97700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2058800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1957500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1877100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1761300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1832800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1690700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1501300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1490600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1618100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>860400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2238,129 +2342,138 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3">
         <v>1400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3300</v>
       </c>
       <c r="H47" s="3">
         <v>3300</v>
       </c>
       <c r="I47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J47" s="3">
         <v>7900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2099300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2067300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2063700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2039000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2008300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1999200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1996300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2012200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>839900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>968800</v>
+      </c>
+      <c r="E49" s="3">
         <v>967600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>954600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>953500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>929000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>928900</v>
       </c>
       <c r="I49" s="3">
         <v>928900</v>
       </c>
       <c r="J49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="K49" s="3">
         <v>929000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>921600</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>899900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,52 +2563,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E52" s="3">
         <v>111600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>115600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>139700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>134000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>136600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>134700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>138000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>50100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,52 +2657,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5290200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5154400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5027300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4911300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4956100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4800000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4608700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4592900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4731600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>2746300</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,272 +2744,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>457900</v>
+      </c>
+      <c r="E57" s="3">
         <v>381900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>364500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>371900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>401200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>368900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>371100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>383100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>474500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>230400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E58" s="3">
         <v>20300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>55600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>61000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>16900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E59" s="3">
         <v>38500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>124700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>46000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>101900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>120600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1046500</v>
+      </c>
+      <c r="E60" s="3">
         <v>943200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>880900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>830100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>945400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>887300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>908600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>834800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>994100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>624800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2263700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2255200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2263000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2226600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2240200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2237900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2327600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2335600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>1251900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>317700</v>
+      </c>
+      <c r="E62" s="3">
         <v>315600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>244900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>253700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>261700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>285600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>299500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>315400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>319600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>157700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,52 +3165,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3605200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3522500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3380900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3346800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3433700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3413100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3446000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3477800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3649200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>2034400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,52 +3419,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E72" s="3">
         <v>456700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>480100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>407200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>365800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>251600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>225300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>182500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>155500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-167200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,52 +3607,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1287900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1238200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1254600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1175200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1131400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1005900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>739900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>699200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>670900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>331600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3701,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>73000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>114200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>42800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>33100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-72500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>148500</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,52 +3821,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E83" s="3">
         <v>36800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>36000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>34700</v>
       </c>
       <c r="J83" s="3">
         <v>34700</v>
       </c>
       <c r="K83" s="3">
+        <v>34700</v>
+      </c>
+      <c r="L83" s="3">
         <v>33300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4101,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E89" s="3">
         <v>154400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>117500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>119600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>89700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>120400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>67500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>96300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,52 +4169,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-68700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4308,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-105400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4182,14 +4415,17 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,52 +4562,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>183400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-119800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-56000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-35900</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4402,54 +4650,60 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E102" s="3">
         <v>68800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-61700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>228600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-64800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-47900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARDT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>ARDT</t>
   </si>
@@ -656,223 +656,236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1601900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1605100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1576700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1645300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1497200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1606300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1449800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1470900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1439000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1346000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1377700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1368700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1092800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1337100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>661400</v>
+      </c>
+      <c r="E9" s="3">
         <v>651400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>677000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>671700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>657700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>654000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>635200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>624100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>621500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>598100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>595600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>598300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>514400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>940400</v>
+      </c>
+      <c r="E10" s="3">
         <v>953700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>899800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>973600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>839600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>952300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>814600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>846900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>817500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>747900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>782100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>770400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>578400</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +903,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -928,17 +942,20 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3">
         <v>2800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,102 +1001,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-21500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-23300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>-8300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>92300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E15" s="3">
         <v>41000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>39200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>39300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>36200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>34700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>33300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1120,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1500300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1560300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1508000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1430100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1448700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1379400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1368900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1363200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1319800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1312700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1291100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1040300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1301800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1244200</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E18" s="3">
         <v>104800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>137300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>67100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>157600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>70400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>102000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>75800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>65000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>77700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>52500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,243 +1240,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>163400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E21" s="3">
         <v>147600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>55600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>176600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>103100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>195300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>107200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>138300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>111200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>100500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>112900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>85800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E22" s="3">
         <v>12400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E23" s="3">
         <v>92400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>122000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>74200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>167200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>57100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>82200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>56600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>67800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-68500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>177900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>51800</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E24" s="3">
         <v>18100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E26" s="3">
         <v>74300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>95700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>59000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>140900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>46000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>67000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>45900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>38700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>55700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-64400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>148500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E27" s="3">
         <v>45000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>73000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>114200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>26300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>42800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>33100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-72500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>148500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,102 +1838,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-163400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E33" s="3">
         <v>45000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>73000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>41400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>114200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>26300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>42800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>33100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-72500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>148500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E35" s="3">
         <v>45000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>73000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>41400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>114200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>26300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>42800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>33100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-72500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>148500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,88 +2135,92 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>609700</v>
+      </c>
+      <c r="E41" s="3">
         <v>709600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>609400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>540600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>495000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>556800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>563100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>334500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>372800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>437600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>59700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E42" s="3">
         <v>2900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>16200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2143,201 +2233,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>721400</v>
+      </c>
+      <c r="E43" s="3">
         <v>771700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>772200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>831600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>829100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>797300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>754900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>762600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>788300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>834600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>532000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E44" s="3">
         <v>118600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>121600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>118400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>120400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>115100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>108200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>105000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>106000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>84800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>401200</v>
+      </c>
+      <c r="E45" s="3">
         <v>343400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>318500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>251000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>177800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>239900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>134900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>148500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>109600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>147200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>97700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2020100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2058800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1957500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1877100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1761300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1832800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1690700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1501300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1490600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1618100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>860400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>18800</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
@@ -2345,135 +2450,144 @@
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>1400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>3300</v>
       </c>
       <c r="I47" s="3">
         <v>3300</v>
       </c>
       <c r="J47" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K47" s="3">
         <v>7900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2142200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2144000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2099300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2067300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2063700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2039000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2008300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1999200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1996300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2012200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>839900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>967600</v>
+      </c>
+      <c r="E49" s="3">
         <v>968800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>967600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>954600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>953500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>929000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>928900</v>
       </c>
       <c r="J49" s="3">
         <v>928900</v>
       </c>
       <c r="K49" s="3">
+        <v>928900</v>
+      </c>
+      <c r="L49" s="3">
         <v>929000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>921600</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>899900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,55 +2683,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E52" s="3">
         <v>111700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>111200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>115600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>134000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>136600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>134700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>138000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>50100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,55 +2783,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5252800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5290200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5154400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5027300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4911300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4956100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4800000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4608700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4592900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4731600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>2746300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,290 +2875,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>419700</v>
+      </c>
+      <c r="E57" s="3">
         <v>457900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>381900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>364500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>371900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>401200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>368900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>371100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>383100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>474500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>230400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E58" s="3">
         <v>76900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>16900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E59" s="3">
         <v>121600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>124700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>46000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>120600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>951500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1046500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>943200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>880900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>830100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>945400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>887300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>908600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>834800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>994100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>624800</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2251900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2241000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2263700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2255200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2263000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2226600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2240200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2237900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2327600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2335600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>1251900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>318200</v>
+      </c>
+      <c r="E62" s="3">
         <v>317700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>315600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>244900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>253700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>261700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>285600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>299500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>315400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>319600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>157700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,55 +3323,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3521600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3605200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3522500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3380900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3346800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3433700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3413100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3446000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3477800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3649200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>2034400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,55 +3593,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>541500</v>
+      </c>
+      <c r="E72" s="3">
         <v>501600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>456700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>480100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>407200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>365800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>251600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>225300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>182500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>155500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-167200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,55 +3793,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1336800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1287900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1238200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1254600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1175200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1131400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1005900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>739900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>699200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>670900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>331600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E81" s="3">
         <v>45000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>73000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>41400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>114200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>26300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>42800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>33100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-72500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>148500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,55 +4020,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E83" s="3">
         <v>37900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>34700</v>
       </c>
       <c r="K83" s="3">
         <v>34700</v>
       </c>
       <c r="L83" s="3">
+        <v>34700</v>
+      </c>
+      <c r="M83" s="3">
         <v>33300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-60200</v>
+      </c>
+      <c r="E89" s="3">
         <v>223400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>154400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>117500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>119600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>89700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>120400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>67500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>96300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,55 +4390,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-84000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-81300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-68700</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-105400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-56700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4418,14 +4652,17 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,55 +4808,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-37000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-25700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>183400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-119800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-56000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4653,57 +4902,63 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-99900</v>
+      </c>
+      <c r="E102" s="3">
         <v>100200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>68800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>45600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-61700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>228600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-64800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-47900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
